--- a/frontend/public/Project_NourishBot.xlsx
+++ b/frontend/public/Project_NourishBot.xlsx
@@ -640,7 +640,7 @@
     <t>Mithra</t>
   </si>
   <si>
-    <t>Dzukku Restaurant</t>
+    <t>NourishBot Kitchen</t>
   </si>
   <si>
     <t>Confirmed</t>
@@ -1738,7 +1738,7 @@
     <t>Management</t>
   </si>
   <si>
-    <t>rajesh.kumar@dzukku.com</t>
+    <t>rajesh.kumar@nourishbot.local</t>
   </si>
   <si>
     <t>HSR Layout, Bangalore</t>
@@ -1768,7 +1768,7 @@
     <t>Kitchen</t>
   </si>
   <si>
-    <t>priya.sharma@dzukku.com</t>
+    <t>priya.sharma@nourishbot.local</t>
   </si>
   <si>
     <t>Koramangala, Bangalore</t>
@@ -1792,7 +1792,7 @@
     <t>Sous Chef</t>
   </si>
   <si>
-    <t>vikram.singh@dzukku.com</t>
+    <t>vikram.singh@nourishbot.local</t>
   </si>
   <si>
     <t>Evening</t>
@@ -1816,7 +1816,7 @@
     <t>Front Desk</t>
   </si>
   <si>
-    <t>anjali.patel@dzukku.com</t>
+    <t>anjali.patel@nourishbot.local</t>
   </si>
   <si>
     <t>Jayanagar, Bangalore</t>
@@ -1840,7 +1840,7 @@
     <t>Delivery</t>
   </si>
   <si>
-    <t>sanjay.reddy@dzukku.com</t>
+    <t>sanjay.reddy@nourishbot.local</t>
   </si>
   <si>
     <t>Mrs. Lakshmi Reddy - 9876543310</t>
@@ -1861,7 +1861,7 @@
     <t>Service</t>
   </si>
   <si>
-    <t>meera.iyer@dzukku.com</t>
+    <t>meera.iyer@nourishbot.local</t>
   </si>
   <si>
     <t>Mr. Ramesh Iyer - 9876543312</t>
@@ -1879,7 +1879,7 @@
     <t>Line Cook</t>
   </si>
   <si>
-    <t>arun.joshi@dzukku.com</t>
+    <t>arun.joshi@nourishbot.local</t>
   </si>
   <si>
     <t>Mrs. Pooja Joshi - 9876543314</t>
@@ -1894,7 +1894,7 @@
     <t>Sunita Malhotra</t>
   </si>
   <si>
-    <t>sunita.malhotra@dzukku.com</t>
+    <t>sunita.malhotra@nourishbot.local</t>
   </si>
   <si>
     <t>Night</t>
@@ -1915,7 +1915,7 @@
     <t>Delivery Driver</t>
   </si>
   <si>
-    <t>rahul.nair@dzukku.com</t>
+    <t>rahul.nair@nourishbot.local</t>
   </si>
   <si>
     <t>Mrs. Geetha Nair - 9876543318</t>
@@ -1933,7 +1933,7 @@
     <t>Prep Cook</t>
   </si>
   <si>
-    <t>kavita.desai@dzukku.com</t>
+    <t>kavita.desai@nourishbot.local</t>
   </si>
   <si>
     <t>Mr. Sanjay Desai - 9876543320</t>
@@ -1948,7 +1948,7 @@
     <t>Manoj Tiwari</t>
   </si>
   <si>
-    <t>manoj.tiwari@dzukku.com</t>
+    <t>manoj.tiwari@nourishbot.local</t>
   </si>
   <si>
     <t>Mrs. Rekha Tiwari - 9876543322</t>
@@ -1960,7 +1960,7 @@
     <t>EMP012</t>
   </si>
   <si>
-    <t>neha.gupta@dzukku.com</t>
+    <t>neha.gupta@nourishbot.local</t>
   </si>
   <si>
     <t>Mr. Anil Gupta - 9876543324</t>
@@ -1978,7 +1978,7 @@
     <t>Tandoor Chef</t>
   </si>
   <si>
-    <t>amit.bose@dzukku.com</t>
+    <t>amit.bose@nourishbot.local</t>
   </si>
   <si>
     <t>Mrs. Smita Bose - 9876543326</t>
@@ -1993,7 +1993,7 @@
     <t>Pooja Reddy</t>
   </si>
   <si>
-    <t>pooja.reddy@dzukku.com</t>
+    <t>pooja.reddy@nourishbot.local</t>
   </si>
   <si>
     <t>Mr. Karthik Reddy - 9876543328</t>
@@ -2008,7 +2008,7 @@
     <t>Rohit Kumar</t>
   </si>
   <si>
-    <t>rohit.kumar@dzukku.com</t>
+    <t>rohit.kumar@nourishbot.local</t>
   </si>
   <si>
     <t>Mrs. Anita Kumar - 9876543330</t>
@@ -2023,7 +2023,7 @@
     <t>Sonia Mehra</t>
   </si>
   <si>
-    <t>sonia.mehra@dzukku.com</t>
+    <t>sonia.mehra@nourishbot.local</t>
   </si>
   <si>
     <t>Mr. Rohan Mehra - 9876543332</t>
@@ -2041,7 +2041,7 @@
     <t>Dishwasher</t>
   </si>
   <si>
-    <t>vishal.nair@dzukku.com</t>
+    <t>vishal.nair@nourishbot.local</t>
   </si>
   <si>
     <t>Mrs. Leela Nair - 9876543334</t>
@@ -2059,7 +2059,7 @@
     <t>Hostess</t>
   </si>
   <si>
-    <t>anita.sharma@dzukku.com</t>
+    <t>anita.sharma@nourishbot.local</t>
   </si>
   <si>
     <t>Mr. Prakash Sharma - 9876543336</t>
@@ -2074,7 +2074,7 @@
     <t>Deepak Singh</t>
   </si>
   <si>
-    <t>deepak.singh@dzukku.com</t>
+    <t>deepak.singh@nourishbot.local</t>
   </si>
   <si>
     <t>Mrs. Maya Singh - 9876543338</t>
@@ -2089,7 +2089,7 @@
     <t>Madhuri Patel</t>
   </si>
   <si>
-    <t>madhuri.patel@dzukku.com</t>
+    <t>madhuri.patel@nourishbot.local</t>
   </si>
   <si>
     <t>Mr. Ajay Patel - 9876543340</t>
